--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484355_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484355_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9976</v>
+        <v>6.4021</v>
       </c>
       <c r="E2" t="n">
-        <v>1.4641</v>
+        <v>2.5963</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5335</v>
+        <v>3.8059</v>
       </c>
       <c r="G2" t="n">
         <v>0.07630000000000001</v>
@@ -610,13 +610,13 @@
         <v>1.5627</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5393</v>
+        <v>0.8653</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0619</v>
+        <v>0.0703</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5226</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>4.8745</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. SEGARRA BAQUES</t>
+          <t>Q. BARDÉS BADIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.466</v>
+        <v>3.0209</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5972</v>
+        <v>1.3149</v>
       </c>
       <c r="F3" t="n">
-        <v>3.8687</v>
+        <v>1.706</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1523</v>
+        <v>0.9782</v>
       </c>
       <c r="H3" t="n">
-        <v>2.0696</v>
+        <v>0.5874</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9173</v>
+        <v>0.3908</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6427</v>
+        <v>1.2074</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8291</v>
+        <v>1.7601</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.1863</v>
+        <v>-0.5527</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5096000000000001</v>
+        <v>-0.2291</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2405</v>
+        <v>-1.1727</v>
       </c>
       <c r="O3" t="n">
-        <v>0.269</v>
+        <v>0.9435</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1488</v>
+        <v>1.7581</v>
       </c>
       <c r="S3" t="n">
-        <v>3.7472</v>
+        <v>-0.0475</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3182</v>
+        <v>0.4396</v>
       </c>
       <c r="U3" t="n">
-        <v>2.429</v>
+        <v>-0.4871</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.6056</v>
+        <v>0.3321</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3869</v>
+        <v>-0.3321</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2186</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>A. BARQUETS ARIZA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8472</v>
+        <v>2.7972</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0322</v>
+        <v>0.4765</v>
       </c>
       <c r="F4" t="n">
-        <v>1.815</v>
+        <v>2.3208</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9782</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5874</v>
+        <v>-1.7347</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3908</v>
+        <v>1.1072</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2074</v>
+        <v>-0.7282</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7601</v>
+        <v>-0.4874</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5527</v>
+        <v>-0.2408</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2291</v>
+        <v>0.1006</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1727</v>
+        <v>-1.2474</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9435</v>
+        <v>1.348</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7581</v>
+        <v>2.5395</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7581</v>
+        <v>2.5395</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2212</v>
+        <v>0.0536</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1569</v>
+        <v>0.3729</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3782</v>
+        <v>-0.3193</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3321</v>
+        <v>0.8317</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3321</v>
+        <v>0.8317</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. ROSADO FORNIES</t>
+          <t>M. SEGARRA BAQUES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2033</v>
+        <v>2.7843</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4964</v>
+        <v>-0.1312</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2931</v>
+        <v>2.9155</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7383</v>
+        <v>1.1523</v>
       </c>
       <c r="H5" t="n">
-        <v>1.199</v>
+        <v>2.0696</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5393</v>
+        <v>-0.9173</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8828</v>
+        <v>0.6427</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8828</v>
+        <v>1.8291</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-1.1863</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1445</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6838</v>
+        <v>0.2405</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5393</v>
+        <v>0.269</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3907</v>
+        <v>2.1488</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0743</v>
+        <v>2.0655</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6136</v>
+        <v>0.5897</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5393</v>
+        <v>1.4758</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.6056</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.3869</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>S. ESTEVES-GARCIA COFFI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9473</v>
+        <v>2.1121</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7864</v>
+        <v>1.1634</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8391999999999999</v>
+        <v>0.9487</v>
       </c>
       <c r="G6" t="n">
-        <v>0.217</v>
+        <v>2.1795</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0939</v>
+        <v>1.3436</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3109</v>
+        <v>0.836</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6465</v>
+        <v>2.2597</v>
       </c>
       <c r="K6" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.8838</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5813</v>
+        <v>1.3758</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4295</v>
+        <v>-0.0801</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1591</v>
+        <v>0.4597</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2704</v>
+        <v>-0.5399</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.586</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="S6" t="n">
-        <v>2.0075</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6208</v>
+        <v>-0.1196</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3867</v>
+        <v>0.6382</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.7731</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. TORRALBA CAROZ</t>
+          <t>M. ROSADO FORNIES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7752</v>
+        <v>1.8594</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9014</v>
+        <v>2.1525</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8738</v>
+        <v>-0.2931</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2315</v>
+        <v>1.7383</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0967</v>
+        <v>1.199</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1348</v>
+        <v>0.5393</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9619</v>
+        <v>1.8828</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9619</v>
+        <v>1.8828</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
+        <v>-0.1445</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.6838</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.5393</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.2696</v>
+      </c>
+      <c r="T7" t="n">
         <v>0.2696</v>
       </c>
-      <c r="N7" t="n">
-        <v>0.1348</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.1348</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.586</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.586</v>
-      </c>
-      <c r="S7" t="n">
-        <v>-0.0424</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-0.0605</v>
-      </c>
       <c r="U7" t="n">
-        <v>0.0182</v>
+        <v>-0.5393</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. BARQUETS ARIZA</t>
+          <t>D. TORRALBA CAROZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7135</v>
+        <v>1.8024</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7163</v>
+        <v>0.9014</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4297</v>
+        <v>0.9011</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6274999999999999</v>
+        <v>1.2315</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7347</v>
+        <v>1.0967</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1072</v>
+        <v>0.1348</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7282</v>
+        <v>0.9619</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4874</v>
+        <v>0.9619</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2408</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1006</v>
+        <v>0.2696</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2474</v>
+        <v>0.1348</v>
       </c>
       <c r="O8" t="n">
-        <v>1.348</v>
+        <v>0.1348</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5395</v>
+        <v>0.586</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5395</v>
+        <v>0.586</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0301</v>
+        <v>-0.0151</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8198</v>
+        <v>-0.0605</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2104</v>
+        <v>0.0454</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8317</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8317</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3985</v>
+        <v>1.5624</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4524</v>
+        <v>1.3712</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0539</v>
+        <v>0.1912</v>
       </c>
       <c r="G9" t="n">
         <v>2.1038</v>
@@ -1156,13 +1156,13 @@
         <v>0.9767</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.428</v>
+        <v>-0.2641</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6357</v>
+        <v>0.5545</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0637</v>
+        <v>-0.8186</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2772</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. ESTEVES-GARCIA COFFI</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.227</v>
+        <v>1.4579</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4962</v>
+        <v>1.9975</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7309</v>
+        <v>-0.5396</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1795</v>
+        <v>0.217</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3436</v>
+        <v>-0.0939</v>
       </c>
       <c r="I10" t="n">
-        <v>0.836</v>
+        <v>0.3109</v>
       </c>
       <c r="J10" t="n">
-        <v>2.2597</v>
+        <v>0.6465</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8838</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3758</v>
+        <v>0.5813</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0801</v>
+        <v>-0.4295</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4597</v>
+        <v>-0.1591</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5399</v>
+        <v>-0.2704</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.586</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3665</v>
+        <v>1.5181</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7868000000000001</v>
+        <v>0.8318</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4203</v>
+        <v>0.6863</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.7731</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X. ALMIRALL CANALS</t>
+          <t>P. ROIG GARCIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9121</v>
+        <v>1.1764</v>
       </c>
       <c r="E11" t="n">
-        <v>1.1134</v>
+        <v>0.4596</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2014</v>
+        <v>0.7167</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2065</v>
+        <v>-0.8078</v>
       </c>
       <c r="H11" t="n">
-        <v>1.0701</v>
+        <v>-0.3226</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8636</v>
+        <v>-0.4852</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1656</v>
+        <v>-0.5981</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0847</v>
+        <v>0.0217</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0809</v>
+        <v>-0.6198</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9591</v>
+        <v>-0.2097</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0146</v>
+        <v>-0.3443</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9445</v>
+        <v>0.1346</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1953</v>
+        <v>0.9767</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1953</v>
+        <v>0.9767</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7874</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0522</v>
+        <v>-0.1609</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8396</v>
+        <v>0.227</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2772</v>
+        <v>0.9414</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X11" t="n">
         <v>-0.2772</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. ROIG GARCIA</t>
+          <t>X. ALMIRALL CANALS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.838</v>
+        <v>0.992</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2574</v>
+        <v>1.2751</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5806</v>
+        <v>-0.2831</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.8078</v>
+        <v>0.2065</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3226</v>
+        <v>1.0701</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4852</v>
+        <v>-0.8636</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5981</v>
+        <v>1.1656</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0217</v>
+        <v>1.0847</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6198</v>
+        <v>0.0809</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2097</v>
+        <v>-0.9591</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3443</v>
+        <v>-0.0146</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1346</v>
+        <v>-0.9445</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2724</v>
+        <v>0.8673999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3631</v>
+        <v>0.1095</v>
       </c>
       <c r="U12" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.7579</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9414</v>
+        <v>-0.2772</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>-0.2772</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.7552</v>
+        <v>-3.1864</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.5402</v>
+        <v>-5.0258</v>
       </c>
       <c r="F13" t="n">
-        <v>1.785</v>
+        <v>1.8394</v>
       </c>
       <c r="G13" t="n">
         <v>-1.3307</v>
@@ -1468,13 +1468,13 @@
         <v>1.1721</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2592</v>
+        <v>-0.172</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8778</v>
+        <v>0.3921</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6186</v>
+        <v>-0.5641</v>
       </c>
       <c r="V13" t="n">
         <v>1.0511</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>21.5705</v>
+        <v>22.7807</v>
       </c>
       <c r="E14" t="n">
-        <v>7.340600000000001</v>
+        <v>8.551399999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>14.2296</v>
+        <v>14.2295</v>
       </c>
       <c r="G14" t="n">
         <v>7.1174</v>
@@ -1531,7 +1531,7 @@
         <v>0.1026000000000002</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.938300000000001</v>
+        <v>-3.9383</v>
       </c>
       <c r="O14" t="n">
         <v>4.0406</v>
@@ -1546,13 +1546,13 @@
         <v>13.674</v>
       </c>
       <c r="S14" t="n">
-        <v>3.9757</v>
+        <v>5.186299999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>2.0787</v>
+        <v>3.289000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>1.897</v>
+        <v>1.8971</v>
       </c>
       <c r="V14" t="n">
         <v>5.5936</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2069</v>
+        <v>2.4395</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1822</v>
+        <v>4.084</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0247</v>
+        <v>-1.6445</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8587</v>
+        <v>3.9917</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0097</v>
+        <v>2.0502</v>
       </c>
       <c r="I15" t="n">
-        <v>0.849</v>
+        <v>1.9416</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2927</v>
+        <v>4.8907</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2522</v>
+        <v>2.9483</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0405</v>
+        <v>1.9424</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.434</v>
+        <v>-0.899</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2425</v>
+        <v>-0.8982</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8085</v>
+        <v>-0.0008</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
         <v>0.9767</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1566</v>
+        <v>-0.3336</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7843</v>
+        <v>0.17</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3723</v>
+        <v>-0.5036</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3869</v>
+        <v>-1.2186</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1097</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5625</v>
+        <v>1.6521</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4667</v>
+        <v>1.3656</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0958</v>
+        <v>0.2864</v>
       </c>
       <c r="G16" t="n">
         <v>1.0701</v>
@@ -1702,13 +1702,13 @@
         <v>0.7814</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5662</v>
+        <v>-0.4767</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1732</v>
+        <v>-0.2743</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.393</v>
+        <v>-0.2023</v>
       </c>
       <c r="V16" t="n">
         <v>0.2772</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5267</v>
+        <v>1.4341</v>
       </c>
       <c r="E17" t="n">
-        <v>3.5784</v>
+        <v>0.5755</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.0516</v>
+        <v>0.8586</v>
       </c>
       <c r="G17" t="n">
-        <v>3.9917</v>
+        <v>0.8587</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0502</v>
+        <v>0.0097</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9416</v>
+        <v>0.849</v>
       </c>
       <c r="J17" t="n">
-        <v>4.8907</v>
+        <v>1.2927</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9483</v>
+        <v>1.2522</v>
       </c>
       <c r="L17" t="n">
-        <v>1.9424</v>
+        <v>0.0405</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.899</v>
+        <v>-0.434</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8982</v>
+        <v>-1.2425</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0008</v>
+        <v>0.8085</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R17" t="n">
         <v>0.9767</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2464</v>
+        <v>0.3838</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3356</v>
+        <v>0.1776</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9108000000000001</v>
+        <v>0.2062</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2186</v>
+        <v>0.3869</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2186</v>
+        <v>0.1097</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1616</v>
+        <v>-0.1343</v>
       </c>
       <c r="E18" t="n">
         <v>-0.1006</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.061</v>
+        <v>-0.0338</v>
       </c>
       <c r="G18" t="n">
         <v>-0.254</v>
@@ -1858,13 +1858,13 @@
         <v>0.1953</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1029</v>
+        <v>-0.0757</v>
       </c>
       <c r="T18" t="n">
         <v>-0.121</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. FONTANALS MARTIN</t>
+          <t>F. ALVAREZ BACO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9333</v>
+        <v>-0.7974</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2634</v>
+        <v>-1.6</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3301</v>
+        <v>0.8026</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4039</v>
+        <v>-1.2588</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6598000000000001</v>
+        <v>0.0494</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2558</v>
+        <v>-1.3081</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0306</v>
+        <v>-0.9687</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6306</v>
+        <v>0.4733</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6613</v>
+        <v>-1.442</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4346</v>
+        <v>-0.29</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0291</v>
+        <v>-0.4239</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4054</v>
+        <v>0.1338</v>
       </c>
       <c r="P19" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4512</v>
+        <v>0.1293</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4345</v>
+        <v>0.3454</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0167</v>
+        <v>-0.2161</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6642</v>
+        <v>0.3321</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. ALVAREZ BACO</t>
+          <t>M. FONTANALS MARTIN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.351</v>
+        <v>-1.0007</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8023</v>
+        <v>-1.4656</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4513</v>
+        <v>0.4649</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2588</v>
+        <v>-0.4039</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0494</v>
+        <v>-0.6598000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3081</v>
+        <v>0.2558</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.9687</v>
+        <v>0.0306</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4733</v>
+        <v>-0.6306</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.442</v>
+        <v>0.6613</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.29</v>
+        <v>-0.4346</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4239</v>
+        <v>-0.0291</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1338</v>
+        <v>-0.4054</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4243</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1432</v>
+        <v>-0.6367</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5675</v>
+        <v>0.1181</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3321</v>
+        <v>-0.6642</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0784</v>
+        <v>-1.0918</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.7806</v>
+        <v>-2.1739</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7023</v>
+        <v>1.0822</v>
       </c>
       <c r="G21" t="n">
         <v>1.9587</v>
@@ -2092,13 +2092,13 @@
         <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9619</v>
+        <v>0.0247</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5777</v>
+        <v>0.029</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3842</v>
+        <v>-0.0043</v>
       </c>
       <c r="V21" t="n">
         <v>0.8317</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>E. MARTÍN GASCÓN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3892</v>
+        <v>-2.4057</v>
       </c>
       <c r="E22" t="n">
-        <v>0.341</v>
+        <v>-2.2481</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.7302</v>
+        <v>-0.1576</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6243</v>
+        <v>-2.4058</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2712</v>
+        <v>-1.3134</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6469</v>
+        <v>-1.0924</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3443</v>
+        <v>-2.2463</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3032</v>
+        <v>-1.0195</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6475</v>
+        <v>-1.2268</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9686</v>
+        <v>-0.1595</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.968</v>
+        <v>-0.2939</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.1344</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8678</v>
+        <v>-1.1404</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6962</v>
+        <v>-0.8335</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1715</v>
+        <v>-0.3069</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.4373</v>
+        <v>0.5545</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2772</v>
+        <v>0.8317</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.7145</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.433</v>
+        <v>-3.0581</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2481</v>
+        <v>-0.1646</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1848</v>
+        <v>-2.8936</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.4058</v>
+        <v>-0.6243</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.3134</v>
+        <v>-1.2712</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.0924</v>
+        <v>0.6469</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.2463</v>
+        <v>0.3443</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.0195</v>
+        <v>-0.3032</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2268</v>
+        <v>0.6475</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1595</v>
+        <v>-0.9686</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2939</v>
+        <v>-0.968</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1344</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>0.586</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R23" t="n">
-        <v>0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1677</v>
+        <v>0.1988</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8335</v>
+        <v>0.1906</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3341</v>
+        <v>0.0081</v>
       </c>
       <c r="V23" t="n">
-        <v>0.5545</v>
+        <v>-2.4373</v>
       </c>
       <c r="W23" t="n">
-        <v>0.8317</v>
+        <v>0.2772</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2772</v>
+        <v>-2.7145</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4748</v>
+        <v>-4.2287</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.8596</v>
+        <v>-2.5562</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6153</v>
+        <v>-1.6724</v>
       </c>
       <c r="G24" t="n">
         <v>-2.3758</v>
@@ -2326,13 +2326,13 @@
         <v>0.7814</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2125</v>
+        <v>0.0337</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6244</v>
+        <v>-0.3211</v>
       </c>
       <c r="U24" t="n">
-        <v>0.412</v>
+        <v>0.3548</v>
       </c>
       <c r="V24" t="n">
         <v>-1.4959</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.631</v>
+        <v>-5.3937</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.3884</v>
+        <v>-3.2873</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.2425</v>
+        <v>-2.1064</v>
       </c>
       <c r="G25" t="n">
         <v>-2.8255</v>
@@ -2404,13 +2404,13 @@
         <v>0.1953</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3329</v>
+        <v>-0.0956</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2145</v>
+        <v>-0.1134</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1183</v>
+        <v>0.0178</v>
       </c>
       <c r="V25" t="n">
         <v>-1.4959</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.4143</v>
+        <v>-7.6373</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.3549</v>
+        <v>-6.6582</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.0594</v>
+        <v>-0.9791</v>
       </c>
       <c r="G26" t="n">
         <v>-4.8485</v>
@@ -2482,13 +2482,13 @@
         <v>0.7814</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5343</v>
+        <v>-0.7573</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.2062</v>
+        <v>-0.5095</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3281</v>
+        <v>-0.2477</v>
       </c>
       <c r="V26" t="n">
         <v>-0.6642</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-21.5705</v>
+        <v>-20.222</v>
       </c>
       <c r="E27" t="n">
-        <v>-14.2296</v>
+        <v>-14.2294</v>
       </c>
       <c r="F27" t="n">
-        <v>-7.3406</v>
+        <v>-5.9927</v>
       </c>
       <c r="G27" t="n">
         <v>-7.117399999999999</v>
@@ -2536,7 +2536,7 @@
         <v>-0.1024000000000007</v>
       </c>
       <c r="K27" t="n">
-        <v>3.938200000000001</v>
+        <v>3.9382</v>
       </c>
       <c r="L27" t="n">
         <v>-4.0404</v>
@@ -2557,16 +2557,16 @@
         <v>-13.6741</v>
       </c>
       <c r="R27" t="n">
-        <v>8.7904</v>
+        <v>8.790399999999998</v>
       </c>
       <c r="S27" t="n">
-        <v>-3.9759</v>
+        <v>-2.6276</v>
       </c>
       <c r="T27" t="n">
         <v>-1.8969</v>
       </c>
       <c r="U27" t="n">
-        <v>-2.0787</v>
+        <v>-0.7305000000000001</v>
       </c>
       <c r="V27" t="n">
         <v>-5.5937</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484355_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484355_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,11 +632,16 @@
       <c r="X2" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484355_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>Q. BARDES BADIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -704,6 +714,11 @@
       </c>
       <c r="X3" t="n">
         <v>0.6642</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484355_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484355_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484355_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484355_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484355_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,11 +1130,16 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484355_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. SELLARÈS GIRALT</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,40 +1151,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5624</v>
+        <v>1.4579</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3712</v>
+        <v>1.9975</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1912</v>
+        <v>-0.5396</v>
       </c>
       <c r="G9" t="n">
-        <v>2.1038</v>
+        <v>0.217</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9304</v>
+        <v>-0.0939</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1733</v>
+        <v>0.3109</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7934</v>
+        <v>0.6465</v>
       </c>
       <c r="K9" t="n">
-        <v>1.6987</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.5813</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3103</v>
+        <v>-0.4295</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7682</v>
+        <v>-0.1591</v>
       </c>
       <c r="O9" t="n">
-        <v>1.0786</v>
+        <v>-0.2704</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1156,28 +1196,33 @@
         <v>0.9767</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2641</v>
+        <v>1.5181</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5545</v>
+        <v>0.8318</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8186</v>
+        <v>0.6863</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2772</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2772</v>
+        <v>-1.7731</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484355_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>P. ROIG GARCIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.4579</v>
+        <v>1.1764</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9975</v>
+        <v>0.4596</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5396</v>
+        <v>0.7167</v>
       </c>
       <c r="G10" t="n">
-        <v>0.217</v>
+        <v>-0.8078</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0939</v>
+        <v>-0.3226</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3109</v>
+        <v>-0.4852</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6465</v>
+        <v>-0.5981</v>
       </c>
       <c r="K10" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.0217</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5813</v>
+        <v>-0.6198</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4295</v>
+        <v>-0.2097</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1591</v>
+        <v>-0.3443</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2704</v>
+        <v>0.1346</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0.9767</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5181</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8318</v>
+        <v>-0.1609</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6863</v>
+        <v>0.227</v>
       </c>
       <c r="V10" t="n">
+        <v>0.9414</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="X10" t="n">
         <v>-0.2772</v>
       </c>
-      <c r="W10" t="n">
-        <v>1.4959</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-1.7731</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484355_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. ROIG GARCIA</t>
+          <t>X. ALMIRALL CANALS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1764</v>
+        <v>0.992</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4596</v>
+        <v>1.2751</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7167</v>
+        <v>-0.2831</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.8078</v>
+        <v>0.2065</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3226</v>
+        <v>1.0701</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4852</v>
+        <v>-0.8636</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5981</v>
+        <v>1.1656</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0217</v>
+        <v>1.0847</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6198</v>
+        <v>0.0809</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2097</v>
+        <v>-0.9591</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3443</v>
+        <v>-0.0146</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1346</v>
+        <v>-0.9445</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="S11" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.8673999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1609</v>
+        <v>0.1095</v>
       </c>
       <c r="U11" t="n">
-        <v>0.227</v>
+        <v>0.7579</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9414</v>
+        <v>-0.2772</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484355_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X. ALMIRALL CANALS</t>
+          <t>M. SELLARES GIRALT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1400,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.992</v>
+        <v>0.9554</v>
       </c>
       <c r="E12" t="n">
-        <v>1.2751</v>
+        <v>0.7642</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2831</v>
+        <v>0.1912</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2065</v>
+        <v>1.4968</v>
       </c>
       <c r="H12" t="n">
-        <v>1.0701</v>
+        <v>0.9304</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8636</v>
+        <v>0.5663</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1656</v>
+        <v>1.1864</v>
       </c>
       <c r="K12" t="n">
-        <v>1.0847</v>
+        <v>1.6987</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0809</v>
+        <v>-0.5122</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.9591</v>
+        <v>0.3103</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0146</v>
+        <v>-0.7682</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.9445</v>
+        <v>1.0786</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1953</v>
+        <v>0.9767</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8673999999999999</v>
+        <v>-0.2641</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1095</v>
+        <v>0.5545</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7579</v>
+        <v>-0.8186</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2772</v>
@@ -1406,12 +1461,17 @@
       </c>
       <c r="X12" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484355_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>M. SELLARÈS GIRALT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1483,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.1864</v>
+        <v>0.607</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.0258</v>
+        <v>0.607</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8394</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.3307</v>
+        <v>0.607</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.9667</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.364</v>
+        <v>0.607</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.5111</v>
+        <v>0.607</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.2034</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.3077</v>
+        <v>0.607</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1804</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7634</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9437</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.7348</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.172</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3921</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5641</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.0511</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.0511</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484355_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,1082 +1566,1393 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>22.7807</v>
+        <v>0.307</v>
       </c>
       <c r="E14" t="n">
-        <v>8.551399999999999</v>
+        <v>0.307</v>
       </c>
       <c r="F14" t="n">
-        <v>14.2295</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>7.1174</v>
+        <v>0.307</v>
       </c>
       <c r="H14" t="n">
-        <v>4.4181</v>
+        <v>0.307</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6993</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>7.0149</v>
+        <v>0.307</v>
       </c>
       <c r="K14" t="n">
-        <v>8.356199999999999</v>
+        <v>0.307</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.3413</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1026000000000002</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.9383</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>4.0406</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>4.883599999999999</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-8.7904</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>13.674</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>5.186299999999999</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.289000000000001</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.8971</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>5.5936</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>7.037599999999999</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.4438</v>
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484355_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>P. CAMPANA SOLER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>TENEA-C.B. ESPARREGUERA</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4395</v>
+        <v>-3.4934</v>
       </c>
       <c r="E15" t="n">
-        <v>4.084</v>
+        <v>-5.3328</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6445</v>
+        <v>1.8394</v>
       </c>
       <c r="G15" t="n">
-        <v>3.9917</v>
+        <v>-1.6377</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0502</v>
+        <v>-1.2737</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9416</v>
+        <v>-0.364</v>
       </c>
       <c r="J15" t="n">
-        <v>4.8907</v>
+        <v>-1.8181</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9483</v>
+        <v>-0.5104</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9424</v>
+        <v>-1.3077</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.899</v>
+        <v>0.1804</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8982</v>
+        <v>-0.7634</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0008</v>
+        <v>0.9437</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-2.7348</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3336</v>
+        <v>-0.172</v>
       </c>
       <c r="T15" t="n">
-        <v>0.17</v>
+        <v>0.3921</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5036</v>
+        <v>-0.5641</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.2186</v>
+        <v>1.0511</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2186</v>
+        <v>1.0511</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484355_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>TENEA-C.B. ESPARREGUERA</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6521</v>
+        <v>22.7807</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3656</v>
+        <v>8.551400000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2864</v>
+        <v>14.2295</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0701</v>
+        <v>7.117399999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4349</v>
+        <v>4.4181</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3648</v>
+        <v>2.6993</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0855</v>
+        <v>7.0149</v>
       </c>
       <c r="K16" t="n">
-        <v>1.045</v>
+        <v>8.356199999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0405</v>
+        <v>-1.3412</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0154</v>
+        <v>0.1026000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3899</v>
+        <v>-3.938300000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4052</v>
+        <v>4.0406</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7814</v>
+        <v>4.883599999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-8.7904</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7814</v>
+        <v>13.674</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4767</v>
+        <v>5.1863</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2743</v>
+        <v>3.289000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2023</v>
+        <v>1.8971</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2772</v>
+        <v>5.5936</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5545</v>
+        <v>7.037599999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2772</v>
-      </c>
+        <v>-1.4438</v>
+      </c>
+      <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4341</v>
+        <v>2.4395</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5755</v>
+        <v>4.084</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8586</v>
+        <v>-1.6445</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8587</v>
+        <v>3.9917</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0097</v>
+        <v>2.0502</v>
       </c>
       <c r="I17" t="n">
-        <v>0.849</v>
+        <v>1.9416</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2927</v>
+        <v>4.8907</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2522</v>
+        <v>2.9483</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0405</v>
+        <v>1.9424</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.434</v>
+        <v>-0.899</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2425</v>
+        <v>-0.8982</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8085</v>
+        <v>-0.0008</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
         <v>0.9767</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3838</v>
+        <v>-0.3336</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1776</v>
+        <v>0.17</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2062</v>
+        <v>-0.5036</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3869</v>
+        <v>-1.2186</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1097</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484355_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. TURNQUEST</t>
+          <t>J. LLORENTE GUILLEMI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1343</v>
+        <v>1.6521</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1006</v>
+        <v>1.3656</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0338</v>
+        <v>0.2864</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.254</v>
+        <v>1.0701</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3888</v>
+        <v>1.4349</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1348</v>
+        <v>-0.3648</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0205</v>
+        <v>1.0855</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0205</v>
+        <v>1.045</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.0405</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2745</v>
+        <v>-0.0154</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4093</v>
+        <v>0.3899</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1348</v>
+        <v>-0.4052</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0757</v>
+        <v>-0.4767</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.121</v>
+        <v>-0.2743</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0454</v>
+        <v>-0.2023</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484355_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. ALVAREZ BACO</t>
+          <t>J. BERTOMEU BALDÉ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7974</v>
+        <v>1.5279</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6</v>
+        <v>1.5279</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8026</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2588</v>
+        <v>1.5279</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0494</v>
+        <v>0.921</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.3081</v>
+        <v>0.607</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9687</v>
+        <v>1.5279</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4733</v>
+        <v>0.921</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.442</v>
+        <v>0.607</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.29</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4239</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1338</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1293</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3454</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2161</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3321</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3321</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484355_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. FONTANALS MARTIN</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0007</v>
+        <v>1.4341</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4656</v>
+        <v>0.5755</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4649</v>
+        <v>0.8586</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4039</v>
+        <v>0.8587</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6598000000000001</v>
+        <v>0.0097</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2558</v>
+        <v>0.849</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0306</v>
+        <v>1.2927</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6306</v>
+        <v>1.2522</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6613</v>
+        <v>0.0405</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4346</v>
+        <v>-0.434</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0291</v>
+        <v>-1.2425</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4054</v>
+        <v>0.8085</v>
       </c>
       <c r="P20" t="n">
-        <v>0.586</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5185999999999999</v>
+        <v>0.3838</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6367</v>
+        <v>0.1776</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1181</v>
+        <v>0.2062</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6642</v>
+        <v>0.3869</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6642</v>
+        <v>0.2772</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.1097</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484355_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. BERTOMEU BALDÉ</t>
+          <t>E. TURNQUEST</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0918</v>
+        <v>-0.1343</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1739</v>
+        <v>-0.1006</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0822</v>
+        <v>-0.0338</v>
       </c>
       <c r="G21" t="n">
-        <v>1.9587</v>
+        <v>-0.254</v>
       </c>
       <c r="H21" t="n">
-        <v>2.309</v>
+        <v>-0.3888</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3504</v>
+        <v>0.1348</v>
       </c>
       <c r="J21" t="n">
-        <v>1.8489</v>
+        <v>0.0205</v>
       </c>
       <c r="K21" t="n">
-        <v>2.603</v>
+        <v>0.0205</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.754</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1098</v>
+        <v>-0.2745</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2939</v>
+        <v>-0.4093</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4037</v>
+        <v>0.1348</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.9069</v>
+        <v>0.1953</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.8836</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0247</v>
+        <v>-0.0757</v>
       </c>
       <c r="T21" t="n">
-        <v>0.029</v>
+        <v>-0.121</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0043</v>
+        <v>0.0454</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8317</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.8317</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484355_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>F. ALVAREZ BACO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4057</v>
+        <v>-0.7974</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2481</v>
+        <v>-1.6</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1576</v>
+        <v>0.8026</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.4058</v>
+        <v>-1.2588</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.3134</v>
+        <v>0.0494</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0924</v>
+        <v>-1.3081</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.2463</v>
+        <v>-0.9687</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.0195</v>
+        <v>0.4733</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2268</v>
+        <v>-1.442</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1595</v>
+        <v>-0.29</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2939</v>
+        <v>-0.4239</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1344</v>
+        <v>0.1338</v>
       </c>
       <c r="P22" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1404</v>
+        <v>0.1293</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8335</v>
+        <v>0.3454</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3069</v>
+        <v>-0.2161</v>
       </c>
       <c r="V22" t="n">
-        <v>0.5545</v>
+        <v>0.3321</v>
       </c>
       <c r="W22" t="n">
-        <v>0.8317</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2772</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484355_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>M. FONTANALS MARTIN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0581</v>
+        <v>-1.0007</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1646</v>
+        <v>-1.4656</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8936</v>
+        <v>0.4649</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.6243</v>
+        <v>-0.4039</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.2712</v>
+        <v>-0.6598000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6469</v>
+        <v>0.2558</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3443</v>
+        <v>0.0306</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3032</v>
+        <v>-0.6306</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6475</v>
+        <v>0.6613</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9686</v>
+        <v>-0.4346</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.968</v>
+        <v>-0.0291</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.4054</v>
       </c>
       <c r="P23" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="Q23" t="n">
         <v>-0.1953</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>-0.9767</v>
       </c>
       <c r="R23" t="n">
         <v>0.7814</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1988</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1906</v>
+        <v>-0.6367</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0081</v>
+        <v>0.1181</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.4373</v>
+        <v>-0.6642</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2772</v>
+        <v>-0.6642</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.7145</v>
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484355_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. PALOMARES MUÑOZ</t>
+          <t>E. MARTIN GASCON</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.2287</v>
+        <v>-2.4057</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.5562</v>
+        <v>-2.2481</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6724</v>
+        <v>-0.1576</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.3758</v>
+        <v>-2.4058</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.5531</v>
+        <v>-1.3134</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8227</v>
+        <v>-1.0924</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.0631</v>
+        <v>-2.2463</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1637</v>
+        <v>-1.0195</v>
       </c>
       <c r="L24" t="n">
         <v>-1.2268</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.3127</v>
+        <v>-0.1595</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.7168</v>
+        <v>-0.2939</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4041</v>
+        <v>0.1344</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0337</v>
+        <v>-1.1404</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3211</v>
+        <v>-0.8335</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3548</v>
+        <v>-0.3069</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.4959</v>
+        <v>0.5545</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.8317</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.4959</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484355_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ SERRANO</t>
+          <t>J. BERTOMEU BALDE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.3937</v>
+        <v>-2.6197</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.2873</v>
+        <v>-3.7019</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.1064</v>
+        <v>1.0822</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.8255</v>
+        <v>0.4307</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.4209</v>
+        <v>1.3881</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4047</v>
+        <v>-0.9574</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.0018</v>
+        <v>0.321</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.3277</v>
+        <v>1.682</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.6741</v>
+        <v>-1.361</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.8237</v>
+        <v>0.1098</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.0931</v>
+        <v>-0.2939</v>
       </c>
       <c r="O25" t="n">
-        <v>0.2694</v>
+        <v>0.4037</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1721</v>
+        <v>-4.8836</v>
       </c>
       <c r="R25" t="n">
-        <v>0.1953</v>
+        <v>0.9767</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0956</v>
+        <v>0.0247</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1134</v>
+        <v>0.029</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0178</v>
+        <v>-0.0043</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.4959</v>
+        <v>0.8317</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>0.8317</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484355_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.6373</v>
+        <v>-3.0581</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.6582</v>
+        <v>-0.1646</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.9791</v>
+        <v>-2.8936</v>
       </c>
       <c r="G26" t="n">
-        <v>-4.8485</v>
+        <v>-0.6243</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.6641</v>
+        <v>-1.2712</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.1844</v>
+        <v>0.6469</v>
       </c>
       <c r="J26" t="n">
-        <v>-3.3357</v>
+        <v>0.3443</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.2868</v>
+        <v>-0.3032</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.0489</v>
+        <v>0.6475</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.5127</v>
+        <v>-0.9686</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.3773</v>
+        <v>-0.968</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.1354</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.3674</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.1488</v>
+        <v>-0.9767</v>
       </c>
       <c r="R26" t="n">
         <v>0.7814</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.7573</v>
+        <v>0.1988</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5095</v>
+        <v>0.1906</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2477</v>
+        <v>0.0081</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.6642</v>
+        <v>-2.4373</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.6642</v>
+        <v>0.2772</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>-2.7145</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484355_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>R. PALOMARES MUNOZ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
+        <v>-4.2287</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-2.5562</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-1.6724</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-2.3758</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-1.5531</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-0.8227</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-1.0631</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.1637</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-1.2268</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-1.3127</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-1.7168</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.4041</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.0337</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.3211</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484355_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>P. MARTINEZ SERRANO</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-5.3937</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-3.2873</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-2.1064</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-2.8255</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-2.4209</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-0.4047</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-2.0018</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-1.3277</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-0.6741</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-0.8237</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-1.0931</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.2694</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="S28" t="n">
+        <v>-0.0956</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-0.1134</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.0178</v>
+      </c>
+      <c r="V28" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>play_by_play_2484355_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>R. FERNANDEZ DIAZ</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-7.6373</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-6.6582</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-0.9791</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-4.8485</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-2.6641</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-2.1844</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-3.3357</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-1.2868</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-2.0489</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-1.5127</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-1.3773</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-0.1354</v>
+      </c>
+      <c r="P29" t="n">
+        <v>-1.3674</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S29" t="n">
+        <v>-0.7573</v>
+      </c>
+      <c r="T29" t="n">
+        <v>-0.5095</v>
+      </c>
+      <c r="U29" t="n">
+        <v>-0.2477</v>
+      </c>
+      <c r="V29" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="W29" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>play_by_play_2484355_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
         <v>-20.222</v>
       </c>
-      <c r="E27" t="n">
-        <v>-14.2294</v>
-      </c>
-      <c r="F27" t="n">
+      <c r="E30" t="n">
+        <v>-14.2295</v>
+      </c>
+      <c r="F30" t="n">
         <v>-5.9927</v>
       </c>
-      <c r="G27" t="n">
-        <v>-7.117399999999999</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-4.4181</v>
-      </c>
-      <c r="I27" t="n">
+      <c r="G30" t="n">
+        <v>-7.1175</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-4.418</v>
+      </c>
+      <c r="I30" t="n">
         <v>-2.6994</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J30" t="n">
         <v>-0.1024000000000007</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K30" t="n">
         <v>3.9382</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L30" t="n">
         <v>-4.0404</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M30" t="n">
         <v>-7.014899999999999</v>
       </c>
-      <c r="N27" t="n">
+      <c r="N30" t="n">
         <v>-8.3561</v>
       </c>
-      <c r="O27" t="n">
+      <c r="O30" t="n">
         <v>1.3413</v>
       </c>
-      <c r="P27" t="n">
+      <c r="P30" t="n">
         <v>-4.883599999999999</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="Q30" t="n">
         <v>-13.6741</v>
       </c>
-      <c r="R27" t="n">
+      <c r="R30" t="n">
         <v>8.790399999999998</v>
       </c>
-      <c r="S27" t="n">
-        <v>-2.6276</v>
-      </c>
-      <c r="T27" t="n">
+      <c r="S30" t="n">
+        <v>-2.627599999999999</v>
+      </c>
+      <c r="T30" t="n">
         <v>-1.8969</v>
       </c>
-      <c r="U27" t="n">
+      <c r="U30" t="n">
         <v>-0.7305000000000001</v>
       </c>
-      <c r="V27" t="n">
+      <c r="V30" t="n">
         <v>-5.5937</v>
       </c>
-      <c r="W27" t="n">
+      <c r="W30" t="n">
         <v>1.4439</v>
       </c>
-      <c r="X27" t="n">
+      <c r="X30" t="n">
         <v>-7.0375</v>
       </c>
+      <c r="Y30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
